--- a/data/trans_orig/ED_ADU-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media del adulto entrevistado</t>
+          <t>Edad media del adulto entrevistado (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,86; 46,76</t>
+          <t>43,89; 46,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,65; 46,71</t>
+          <t>43,59; 46,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,85; 48,7</t>
+          <t>45,76; 48,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,38; 52,63</t>
+          <t>49,65; 52,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,56</t>
+          <t>40,49; 43,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,27; 42,46</t>
+          <t>39,29; 42,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,27; 45,54</t>
+          <t>42,23; 45,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,32; 49,01</t>
+          <t>46,18; 48,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,81; 45,06</t>
+          <t>42,97; 45,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,26; 44,37</t>
+          <t>42,25; 44,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,54; 46,82</t>
+          <t>44,64; 46,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,39; 50,45</t>
+          <t>48,51; 50,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,52; 46,76</t>
+          <t>43,64; 47,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,26; 47,48</t>
+          <t>44,51; 47,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,64; 48,67</t>
+          <t>45,57; 48,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,36; 52,76</t>
+          <t>49,34; 52,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,69; 38,42</t>
+          <t>35,59; 38,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,98; 42,88</t>
+          <t>40,08; 42,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,82; 44,58</t>
+          <t>41,85; 44,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,24; 47,75</t>
+          <t>45,15; 47,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,94; 42,14</t>
+          <t>39,9; 42,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,79; 45,06</t>
+          <t>42,84; 45,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,05; 46,16</t>
+          <t>44,02; 46,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,77; 49,95</t>
+          <t>47,85; 50,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,63; 46,36</t>
+          <t>43,77; 46,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,03; 48,74</t>
+          <t>46,05; 48,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,52; 52,27</t>
+          <t>49,49; 52,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,44; 53,25</t>
+          <t>50,67; 53,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,91; 47,53</t>
+          <t>43,14; 47,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,43; 50,86</t>
+          <t>46,28; 50,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,82; 54,92</t>
+          <t>48,91; 54,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,87; 57,77</t>
+          <t>52,81; 57,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,87; 46,19</t>
+          <t>43,86; 46,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,51; 48,94</t>
+          <t>46,58; 48,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,83; 52,51</t>
+          <t>49,83; 52,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,23; 53,9</t>
+          <t>51,34; 53,77</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,92; 47,9</t>
+          <t>45,91; 47,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,35; 48,52</t>
+          <t>46,45; 48,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,3; 49,22</t>
+          <t>47,22; 49,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,13; 51,89</t>
+          <t>49,16; 51,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,13; 43,59</t>
+          <t>41,15; 43,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,98; 42,12</t>
+          <t>39,98; 42,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,79; 44,06</t>
+          <t>41,81; 44,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,56; 58,73</t>
+          <t>46,49; 57,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,39; 46,0</t>
+          <t>44,33; 45,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,14; 45,66</t>
+          <t>44,11; 45,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,26; 46,71</t>
+          <t>45,22; 46,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,66; 55,4</t>
+          <t>48,64; 55,75</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,6; 45,55</t>
+          <t>41,43; 45,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,85; 48,21</t>
+          <t>44,93; 48,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,62; 49,63</t>
+          <t>46,69; 49,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,39; 51,4</t>
+          <t>47,63; 51,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,93; 47,79</t>
+          <t>44,85; 47,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,11; 51,77</t>
+          <t>49,21; 51,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,71; 52,3</t>
+          <t>49,57; 52,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,37; 54,59</t>
+          <t>47,85; 54,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,09; 46,44</t>
+          <t>44,16; 46,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,88; 49,92</t>
+          <t>47,9; 49,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,71; 50,7</t>
+          <t>48,72; 50,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,51; 52,89</t>
+          <t>48,61; 52,89</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,3; 22,4</t>
+          <t>20,27; 22,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,14; 22,08</t>
+          <t>20,15; 22,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,39; 22,03</t>
+          <t>20,49; 22,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,22; 23,9</t>
+          <t>21,26; 24,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,98; 52,3</t>
+          <t>49,97; 52,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,55; 53,3</t>
+          <t>50,69; 53,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,63; 54,39</t>
+          <t>51,59; 54,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,33; 56,29</t>
+          <t>52,43; 56,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,23; 46,51</t>
+          <t>44,28; 46,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,7; 47,44</t>
+          <t>44,67; 47,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44,98; 47,8</t>
+          <t>45,04; 47,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,57; 48,56</t>
+          <t>44,78; 48,45</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,81; 44,02</t>
+          <t>42,8; 43,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,19; 45,44</t>
+          <t>44,23; 45,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,44; 46,66</t>
+          <t>45,42; 46,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,0; 49,61</t>
+          <t>47,99; 49,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,22; 46,46</t>
+          <t>45,08; 46,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,42; 47,65</t>
+          <t>46,34; 47,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,54; 48,92</t>
+          <t>47,59; 48,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,14; 54,32</t>
+          <t>50,08; 54,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,2; 45,08</t>
+          <t>44,19; 45,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,46; 46,33</t>
+          <t>45,51; 46,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,71; 47,6</t>
+          <t>46,75; 47,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,35; 51,71</t>
+          <t>49,4; 51,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_ADU-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51,17</t>
+          <t>51,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,61</t>
+          <t>47,97</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,5</t>
+          <t>49,72</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,89; 46,69</t>
+          <t>43,9; 46,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,59; 46,65</t>
+          <t>43,71; 46,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,76; 48,79</t>
+          <t>45,8; 48,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,65; 52,59</t>
+          <t>49,77; 52,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,49; 43,67</t>
+          <t>40,34; 43,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,29; 42,57</t>
+          <t>39,32; 42,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,23; 45,68</t>
+          <t>42,35; 45,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,18; 48,78</t>
+          <t>46,54; 49,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,97; 45,04</t>
+          <t>42,98; 45,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,25; 44,46</t>
+          <t>42,22; 44,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,64; 46,85</t>
+          <t>44,59; 46,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,51; 50,47</t>
+          <t>48,71; 50,68</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,04</t>
+          <t>51,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,5</t>
+          <t>46,88</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,96</t>
+          <t>49,31</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,64; 47,02</t>
+          <t>43,5; 46,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,51; 47,62</t>
+          <t>44,23; 47,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,57; 48,47</t>
+          <t>45,52; 48,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,34; 52,73</t>
+          <t>49,89; 53,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,59; 38,3</t>
+          <t>35,64; 38,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,08; 42,89</t>
+          <t>40,0; 42,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,85; 44,61</t>
+          <t>41,9; 44,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,15; 47,81</t>
+          <t>45,55; 48,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,9; 42,1</t>
+          <t>39,94; 42,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,84; 45,01</t>
+          <t>42,73; 45,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,02; 46,08</t>
+          <t>44,0; 46,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,85; 50,0</t>
+          <t>48,25; 50,51</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,81</t>
+          <t>52,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,37</t>
+          <t>55,06</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,52</t>
+          <t>52,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,77; 46,34</t>
+          <t>43,69; 46,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,05; 48,87</t>
+          <t>46,23; 48,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,49; 52,35</t>
+          <t>49,53; 52,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,67; 53,14</t>
+          <t>50,59; 53,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,14; 47,54</t>
+          <t>42,87; 47,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,28; 50,58</t>
+          <t>46,28; 50,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,91; 54,88</t>
+          <t>48,68; 54,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,81; 57,79</t>
+          <t>52,6; 57,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,86; 46,35</t>
+          <t>43,9; 46,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,58; 48,92</t>
+          <t>46,57; 48,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,83; 52,41</t>
+          <t>49,8; 52,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,34; 53,77</t>
+          <t>51,73; 54,24</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,42</t>
+          <t>50,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,12</t>
+          <t>46,7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,76</t>
+          <t>48,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,91; 47,93</t>
+          <t>45,87; 48,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,45; 48,64</t>
+          <t>46,45; 48,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,22; 49,26</t>
+          <t>47,23; 49,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,16; 51,82</t>
+          <t>48,98; 51,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,15; 43,68</t>
+          <t>41,08; 43,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,98; 42,16</t>
+          <t>39,96; 42,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,81; 44,09</t>
+          <t>41,81; 44,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,49; 57,46</t>
+          <t>45,57; 47,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,33; 45,94</t>
+          <t>44,37; 46,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,11; 45,74</t>
+          <t>44,16; 45,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,22; 46,69</t>
+          <t>45,26; 46,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,64; 55,75</t>
+          <t>47,8; 49,5</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,66</t>
+          <t>48,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52,53</t>
+          <t>53,68</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,49</t>
+          <t>51,58</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,43; 45,58</t>
+          <t>41,57; 45,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,93; 48,34</t>
+          <t>44,96; 48,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,69; 49,56</t>
+          <t>46,52; 49,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,63; 51,43</t>
+          <t>46,9; 50,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,85; 47,73</t>
+          <t>44,99; 47,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,21; 51,97</t>
+          <t>49,31; 51,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,57; 52,29</t>
+          <t>49,8; 52,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,85; 54,68</t>
+          <t>52,62; 54,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,16; 46,52</t>
+          <t>44,12; 46,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,9; 49,97</t>
+          <t>47,97; 49,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,72; 50,62</t>
+          <t>48,53; 50,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,61; 52,89</t>
+          <t>50,6; 52,47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,38</t>
+          <t>22,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>54,27</t>
+          <t>53,46</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,61</t>
+          <t>46,72</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,27; 22,51</t>
+          <t>20,25; 22,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,15; 22,1</t>
+          <t>20,16; 22,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,0</t>
+          <t>20,45; 22,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,26; 24,06</t>
+          <t>21,5; 24,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,97; 52,39</t>
+          <t>50,1; 52,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,69; 53,4</t>
+          <t>50,52; 53,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,59; 54,51</t>
+          <t>51,6; 54,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,43; 56,07</t>
+          <t>51,77; 55,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,28; 46,5</t>
+          <t>44,24; 46,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,67; 47,3</t>
+          <t>44,72; 47,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45,04; 47,72</t>
+          <t>44,86; 47,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,78; 48,45</t>
+          <t>44,78; 48,4</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48,79</t>
+          <t>48,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>51,39</t>
+          <t>50,49</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,12</t>
+          <t>49,6</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,8; 43,99</t>
+          <t>42,75; 44,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,23; 45,41</t>
+          <t>44,14; 45,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,42; 46,63</t>
+          <t>45,41; 46,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,99; 49,61</t>
+          <t>47,95; 49,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,08; 46,36</t>
+          <t>45,14; 46,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,34; 47,66</t>
+          <t>46,4; 47,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,59; 48,95</t>
+          <t>47,62; 48,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,08; 54,14</t>
+          <t>49,88; 51,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,19; 45,05</t>
+          <t>44,18; 45,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,51; 46,35</t>
+          <t>45,49; 46,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,75; 47,61</t>
+          <t>46,71; 47,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,4; 51,95</t>
+          <t>49,09; 50,05</t>
         </is>
       </c>
     </row>
